--- a/plantillas/55.xlsx
+++ b/plantillas/55.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$3</definedName>
     <definedName name="MARCA_2">Listas!$E$2:$E$5</definedName>
-    <definedName name="MARCA_3">Listas!$F$2:$F$16</definedName>
+    <definedName name="MARCA_3">Listas!$F$2:$F$15</definedName>
     <definedName name="MARCA_4">Listas!$G$2:$G$8</definedName>
     <definedName name="MARCA_5">Listas!$H$2:$H$2</definedName>
-    <definedName name="MARCA_6">Listas!$I$2:$I$5</definedName>
+    <definedName name="MARCA_6">Listas!$I$2:$I$6</definedName>
     <definedName name="MARCA_7">Listas!$J$2:$J$2</definedName>
     <definedName name="MARCA_8">Listas!$K$2:$K$2</definedName>
     <definedName name="MARCA_9">Listas!$L$2:$L$2</definedName>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -8849,12 +8849,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 4KG · 93512380000</t>
+          <t>DOG CHOW CACHORRO RAZA MD/GR 4KG · 93512540000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -8921,7 +8926,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA MD/GR 4KG · 93512540000</t>
+          <t>DOG CHOW CACHORRO RAZA MD/GRD 2KG · 93512530000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8983,7 +8988,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA MD/GRD 2KG · 93512530000</t>
+          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -9045,7 +9050,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
+          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -9092,7 +9097,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
+          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -9129,7 +9134,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
+          <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -9161,7 +9166,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
+          <t>DOG CHOW POLLO POUCH 100G MX · 90038270000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -9193,7 +9198,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DOG CHOW POLLO POUCH 100G MX · 90038270000</t>
+          <t>DOG CHOW POLLO Y CARNE POUCH 100G MX · 90038280000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -9225,7 +9230,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DOG CHOW POLLO Y CARNE POUCH 100G MX · 90038280000</t>
+          <t>DOG CHOW RAZAS PEQUENAS CARNE POUCH 100G · 90038320000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -9252,7 +9257,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DOG CHOW RAZAS PEQUENAS CARNE POUCH 100G · 90038320000</t>
+          <t>DOG CHOW RAZAS PEQUENAS CORDERO POUCH 10 · 90038310000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -9275,11 +9280,6 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>MARCA_15</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DOG CHOW RAZAS PEQUENAS CORDERO POUCH 10 · 90038310000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -9658,12 +9658,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 4KG · 93512380000</t>
+          <t>DOG CHOW CACHORRO RAZA MD/GR 4KG · 93512540000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93512380000</t>
+          <t>93512540000</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -9678,16 +9678,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA MD/GR 4KG · 93512540000</t>
+          <t>DOG CHOW CACHORRO RAZA MD/GRD 2KG · 93512530000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93512540000</t>
+          <t>93512530000</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9698,12 +9698,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA MD/GRD 2KG · 93512530000</t>
+          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>93512530000</t>
+          <t>93512550000</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -9718,16 +9718,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
+          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>93512550000</t>
+          <t>90038330000</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9738,16 +9738,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
+          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90038330000</t>
+          <t>90038300000</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9758,16 +9758,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
+          <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90038300000</t>
+          <t>90038290000</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9778,16 +9778,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
+          <t>DOG CHOW POLLO POUCH 100G MX · 90038270000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90038290000</t>
+          <t>90038270000</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9798,16 +9798,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DOG CHOW POLLO POUCH 100G MX · 90038270000</t>
+          <t>DOG CHOW POLLO Y CARNE POUCH 100G MX · 90038280000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90038270000</t>
+          <t>90038280000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9818,16 +9818,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DOG CHOW POLLO Y CARNE POUCH 100G MX · 90038280000</t>
+          <t>DOG CHOW RAZAS PEQUENAS CARNE POUCH 100G · 90038320000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90038280000</t>
+          <t>90038320000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9838,16 +9838,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DOG CHOW RAZAS PEQUENAS CARNE POUCH 100G · 90038320000</t>
+          <t>DOG CHOW RAZAS PEQUENAS CORDERO POUCH 10 · 90038310000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90038320000</t>
+          <t>90038310000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9858,36 +9858,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DOG CHOW RAZAS PEQUENAS CORDERO POUCH 10 · 90038310000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90038310000</t>
+          <t>90038450000</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90038450000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9898,16 +9898,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038510000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9918,16 +9918,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90038510000</t>
+          <t>90038520000</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9938,16 +9938,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90038520000</t>
+          <t>90038550000</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9958,12 +9958,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90038550000</t>
+          <t>93502660000</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -9978,16 +9978,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93502660000</t>
+          <t>93502650000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9998,56 +9998,56 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
+          <t>GATI PESCADO 6.6LB · 93519150000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93502650000</t>
+          <t>93519150000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GATI PESCADO 6.6LB · 93519150000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93519150000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10058,16 +10058,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10078,12 +10078,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -10187,7 +10187,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/55.xlsx
+++ b/plantillas/55.xlsx
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/55.xlsx
+++ b/plantillas/55.xlsx
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
